--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T15:25:29+00:00</t>
+    <t>2024-10-26T11:41:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T11:41:35+00:00</t>
+    <t>2024-10-26T12:52:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:52:52+00:00</t>
+    <t>2024-10-26T13:45:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="235">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:45:19+00:00</t>
+    <t>2024-10-26T13:53:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -339,6 +339,22 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Address.extension:municipalityCode</t>
+  </si>
+  <si>
+    <t>municipalityCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode}
+</t>
+  </si>
+  <si>
+    <t>Address Municipality Code</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
   </si>
   <si>
     <t>Address.use</t>
@@ -1034,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.23046875" customWidth="true" bestFit="true"/>
@@ -1545,9 +1561,11 @@
         <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="D5" t="s" s="2">
         <v>21</v>
       </c>
@@ -1562,10 +1580,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>108</v>
@@ -1576,12 +1594,8 @@
       <c r="M5" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
       </c>
@@ -1593,7 +1607,7 @@
         <v>21</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="U5" t="s" s="2">
         <v>21</v>
@@ -1605,13 +1619,13 @@
         <v>21</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>21</v>
@@ -1629,28 +1643,28 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>21</v>
@@ -1658,10 +1672,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1678,24 +1692,26 @@
         <v>21</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="O6" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="O6" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="P6" t="s" s="2">
         <v>21</v>
       </c>
@@ -1707,7 +1723,7 @@
         <v>21</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="U6" t="s" s="2">
         <v>21</v>
@@ -1719,13 +1735,13 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
@@ -1743,7 +1759,7 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1755,27 +1771,27 @@
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1795,23 +1811,21 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>21</v>
       </c>
@@ -1823,7 +1837,7 @@
         <v>21</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="U7" t="s" s="2">
         <v>21</v>
@@ -1835,13 +1849,13 @@
         <v>21</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>21</v>
@@ -1859,7 +1873,7 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1871,27 +1885,27 @@
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1902,7 +1916,7 @@
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -1911,19 +1925,23 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O8" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="P8" t="s" s="2">
         <v>21</v>
       </c>
@@ -1935,75 +1953,75 @@
         <v>21</v>
       </c>
       <c r="T8" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="U8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AK8" t="s" s="2">
+      <c r="AM8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2014,7 +2032,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2023,16 +2041,16 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="K9" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2047,7 +2065,7 @@
         <v>21</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="U9" t="s" s="2">
         <v>21</v>
@@ -2083,39 +2101,39 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2126,7 +2144,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -2138,13 +2156,13 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2183,29 +2201,31 @@
         <v>21</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AC10" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -2222,14 +2242,12 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2238,7 +2256,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2250,13 +2268,13 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2295,16 +2313,14 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>104</v>
@@ -2325,7 +2341,7 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>21</v>
@@ -2339,10 +2355,10 @@
         <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -2364,13 +2380,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2439,7 +2455,7 @@
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>21</v>
@@ -2450,13 +2466,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>21</v>
@@ -2478,10 +2494,10 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>167</v>
@@ -2567,7 +2583,7 @@
         <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>170</v>
@@ -2598,7 +2614,7 @@
         <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2658,7 +2674,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -2667,7 +2683,7 @@
         <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -2681,9 +2697,11 @@
         <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2704,13 +2722,13 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2734,7 +2752,7 @@
         <v>21</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
         <v>21</v>
@@ -2761,19 +2779,19 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>21</v>
@@ -2797,7 +2815,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2813,16 +2831,16 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2837,43 +2855,43 @@
         <v>21</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2885,38 +2903,38 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -2925,20 +2943,18 @@
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -2951,7 +2967,7 @@
         <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>21</v>
@@ -2987,7 +3003,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -2999,38 +3015,38 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3039,18 +3055,20 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3063,7 +3081,7 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>21</v>
@@ -3099,7 +3117,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3111,31 +3129,31 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>201</v>
-      </c>
       <c r="AM18" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3151,16 +3169,16 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3175,7 +3193,7 @@
         <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>21</v>
@@ -3211,7 +3229,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3223,31 +3241,31 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3263,20 +3281,18 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3289,7 +3305,7 @@
         <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>21</v>
@@ -3325,7 +3341,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3337,27 +3353,27 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3368,7 +3384,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3377,21 +3393,21 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3403,7 +3419,7 @@
         <v>21</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>21</v>
@@ -3439,7 +3455,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3451,18 +3467,132 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="L22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="P22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>21</v>
       </c>
     </row>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:53:56+00:00</t>
+    <t>2024-10-31T15:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:15:50+00:00</t>
+    <t>2024-11-17T20:36:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:36:22+00:00</t>
+    <t>2024-11-17T21:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:00:03+00:00</t>
+    <t>2024-11-17T21:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:23:25+00:00</t>
+    <t>2024-11-27T13:38:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:38:13+00:00</t>
+    <t>2024-12-15T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T13:48:39+00:00</t>
+    <t>2024-12-19T09:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-19T09:41:53+00:00</t>
+    <t>2025-01-08T15:19:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T15:19:00+00:00</t>
+    <t>2025-01-24T15:25:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:25:06+00:00</t>
+    <t>2025-01-27T07:42:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T07:42:42+00:00</t>
+    <t>2025-01-27T10:22:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T10:22:54+00:00</t>
+    <t>2025-01-27T12:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-01T11:26:35+00:00</t>
+    <t>2026-08-11T10:57:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2446,7 +2446,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>105</v>
@@ -2560,7 +2560,7 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>105</v>
@@ -2674,7 +2674,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:57:38+00:00</t>
+    <t>2026-08-11T12:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
     <t>municipalityCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityCode}
 </t>
   </si>
   <si>
@@ -557,7 +557,7 @@
     <t>additionalInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-additionalInformation}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-additionalInformation}
 </t>
   </si>
   <si>
@@ -1063,7 +1063,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="92.1484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.4921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-core-main/StructureDefinition-at-core-address.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T12:53:53+00:00</t>
+    <t>2026-08-20T09:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
